--- a/app/content/xie.xlsx
+++ b/app/content/xie.xlsx
@@ -1250,7 +1250,7 @@
         <v>温言宽慰</v>
       </c>
       <c r="C2" t="str">
-        <v>情</v>
+        <v>策</v>
       </c>
       <c r="D2" t="str">
         <v>先顺着老人的怕，再说你的来意。</v>
@@ -1261,8 +1261,8 @@
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="G2">
-        <v>1</v>
+      <c r="G2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1273,7 +1273,7 @@
         <v>不动声色</v>
       </c>
       <c r="C3" t="str">
-        <v>理</v>
+        <v>势</v>
       </c>
       <c r="D3" t="str">
         <v>不问案子，只问当日天光、街巷。</v>
@@ -1296,7 +1296,7 @@
         <v>亮明官身</v>
       </c>
       <c r="C4" t="str">
-        <v>威</v>
+        <v>势</v>
       </c>
       <c r="D4" t="str">
         <v>出示官牒，正色相询。</v>
@@ -1307,8 +1307,8 @@
       <c r="F4">
         <v>4</v>
       </c>
-      <c r="G4">
-        <v>3</v>
+      <c r="G4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -1319,7 +1319,7 @@
         <v>隐于夜色</v>
       </c>
       <c r="C5" t="str">
-        <v>威</v>
+        <v>隐</v>
       </c>
       <c r="D5" t="str">
         <v>布衣独行，不叫任何人认出你。</v>
@@ -1330,8 +1330,8 @@
       <c r="F5">
         <v>2</v>
       </c>
-      <c r="G5">
-        <v>1</v>
+      <c r="G5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1342,7 +1342,7 @@
         <v>许以安宁</v>
       </c>
       <c r="C6" t="str">
-        <v>利</v>
+        <v>策</v>
       </c>
       <c r="D6" t="str">
         <v>担保说出实情者，不受牵连。</v>
@@ -1365,7 +1365,7 @@
         <v>提及亡者</v>
       </c>
       <c r="C7" t="str">
-        <v>情</v>
+        <v>隐</v>
       </c>
       <c r="D7" t="str">
         <v>说起那个白衣书生，说他的诗。</v>
@@ -1387,6 +1387,9 @@
       <c r="B8" t="str">
         <v>凸面镜片</v>
       </c>
+      <c r="C8" t="str">
+        <v>器</v>
+      </c>
       <c r="D8" t="str">
         <v>对局中亮出：西洋聚光镜片——一切「天火」谎言在它面前自燃。</v>
       </c>
@@ -1407,6 +1410,9 @@
       <c r="B9" t="str">
         <v>白磷残粉</v>
       </c>
+      <c r="C9" t="str">
+        <v>器</v>
+      </c>
       <c r="D9" t="str">
         <v>对局中使用：袖口蜡脂的真相在手，下一言掷地有声。（成术+3）</v>
       </c>
@@ -1427,6 +1433,9 @@
       <c r="B10" t="str">
         <v>织妇的木梭</v>
       </c>
+      <c r="C10" t="str">
+        <v>器</v>
+      </c>
       <c r="D10" t="str">
         <v>对局中出示：她递给你的旧梭——「大人，替那条街的人，多问一句。」</v>
       </c>
@@ -1447,6 +1456,9 @@
       <c r="B11" t="str">
         <v>谢亮诗稿</v>
       </c>
+      <c r="C11" t="str">
+        <v>器</v>
+      </c>
       <c r="D11" t="str">
         <v>对局中使用：临窗吟诵的手稿，念之令人心神一凛，再抽两张牌。</v>
       </c>
@@ -1467,6 +1479,9 @@
       <c r="B12" t="str">
         <v>温过的夜酒</v>
       </c>
+      <c r="C12" t="str">
+        <v>器</v>
+      </c>
       <c r="D12" t="str">
         <v>对局中使用：深夜公堂的旧习——只饮这一盏。（+3）</v>
       </c>
@@ -1487,8 +1502,11 @@
       <c r="B13" t="str">
         <v>檐下织妇</v>
       </c>
+      <c r="C13" t="str">
+        <v>势</v>
+      </c>
       <c r="D13" t="str">
-        <v>携带：情牌 +1。整条街巷最沉默通透的旁观者。</v>
+        <v>携带：策牌 +1。整条街巷最沉默通透的旁观者。</v>
       </c>
       <c r="E13" t="str">
         <v>「老朽躲在檐下避热织布——恍惚望见高墙之上，立着一道素衣人影。」</v>
@@ -1507,6 +1525,9 @@
       <c r="B14" t="str">
         <v>酒摊赵听风</v>
       </c>
+      <c r="C14" t="str">
+        <v>势</v>
+      </c>
       <c r="D14" t="str">
         <v>携带：气力上限 +2。胆小，但眼睛没坏。</v>
       </c>
@@ -1527,8 +1548,11 @@
       <c r="B15" t="str">
         <v>客商安德烈</v>
       </c>
+      <c r="C15" t="str">
+        <v>势</v>
+      </c>
       <c r="D15" t="str">
-        <v>携带：理牌 +1。暴躁的西洋人，记性却好得吓人。</v>
+        <v>携带：器牌 +1。暴躁的西洋人，记性却好得吓人。</v>
       </c>
       <c r="E15" t="str">
         <v>他记得每一单镜片的出货——包括那一单，买主没有露面。</v>
@@ -1547,8 +1571,11 @@
       <c r="B16" t="str">
         <v>都头雷如</v>
       </c>
+      <c r="C16" t="str">
+        <v>势</v>
+      </c>
       <c r="D16" t="str">
-        <v>携带：利牌 +1。账目异常暴富的库房都头。</v>
+        <v>携带：策牌 +1。账目异常暴富的库房都头。</v>
       </c>
       <c r="E16" t="str">
         <v>他连证物都敢卖。卖你几句真话，不亏。</v>
@@ -1567,6 +1594,9 @@
       <c r="B17" t="str">
         <v>铜钱一串</v>
       </c>
+      <c r="C17" t="str">
+        <v>器</v>
+      </c>
       <c r="D17" t="str">
         <v>资源卡：翻到即入钱袋。</v>
       </c>
@@ -1586,6 +1616,9 @@
       </c>
       <c r="B18" t="str">
         <v>驿银三十两</v>
+      </c>
+      <c r="C18" t="str">
+        <v>器</v>
       </c>
       <c r="D18" t="str">
         <v>资源卡：翻到即入钱袋。</v>
@@ -1862,7 +1895,7 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>情,理,情,威,理,利,情</v>
+        <v>策,策,隐,势,策,策,策</v>
       </c>
       <c r="I2" t="str">
         <v/>
